--- a/historical_data/analysis/wind and solar historical capacity summary PT.xlsx
+++ b/historical_data/analysis/wind and solar historical capacity summary PT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bluepp-my.sharepoint.com/personal/xfsf_bpp-projects_com/Documents/Documents/GitHub/Speciale/Historical Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bluepp-my.sharepoint.com/personal/xfsf_bpp-projects_com/Documents/Documents/GitHub/Speciale/historical_data/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{B68D7143-65A9-4709-8DA8-34E442F0ACDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61DFCB49-E4C4-4BEF-BA55-7868B95BD800}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61DFCB49-E4C4-4BEF-BA55-7868B95BD800}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -112,13 +112,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2860,31 +2859,31 @@
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>2015</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>2016</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>2017</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <v>2018</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>2019</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5">
         <v>2020</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>2021</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5">
         <v>2022</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5">
         <v>2023</v>
       </c>
       <c r="K5">
@@ -2898,31 +2897,31 @@
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>447</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>512.82399999999996</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>579.23599999999999</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>667.43100000000004</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>901.43799999999999</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>1100.2919999999999</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <v>1645.9939999999999</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="3">
         <v>2646.2570000000001</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>3868.7910000000002</v>
       </c>
     </row>
@@ -2968,7 +2967,7 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>369</v>
       </c>
       <c r="C8">
@@ -3116,7 +3115,7 @@
       <c r="A14" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>4192</v>
       </c>
       <c r="C14">
@@ -3148,7 +3147,7 @@
       </c>
     </row>
     <row r="25" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F25" s="5"/>
+      <c r="F25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
